--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:15:06+05:30</t>
+    <t>2026-05-13T15:29:14+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:29:14+05:30</t>
+    <t>2026-05-15T09:21:03+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A categorization or tagging label associated with an Attachment.
+    <t>A categorization or semantic tag associated with an Attachment.
 This extension allows multiple tags to be associated with an
-Attachment for workflow, classification, indexing, or retrieval
-purposes.</t>
+Attachment for workflow, classification, indexing, retrieval,
+processing, or application behavior purposes.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -338,11 +338,18 @@
 </t>
   </si>
   <si>
-    <t>Categorization tag for the attachment</t>
+    <t>Semantic categorization tag for the attachment</t>
   </si>
   <si>
     <t>Represents a semantic classification, workflow label,
-or categorization tag associated with the attachment.</t>
+behavioral indicator, or categorization tag associated
+with the attachment.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/attachment-tag</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -686,7 +693,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.3125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -1287,13 +1294,11 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1323,7 +1328,7 @@
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>101</v>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:21:03+05:30</t>
+    <t>2026-05-16T07:30:07+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T07:30:07+05:30</t>
+    <t>2026-05-16T10:04:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:04:42+05:30</t>
+    <t>2026-05-16T10:41:11+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T10:41:11+05:30</t>
+    <t>2026-05-16T12:18:43+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:18:43+05:30</t>
+    <t>2026-05-16T12:58:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,7 +334,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 </t>
   </si>
   <si>
@@ -678,7 +678,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.1015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-attachment-tag.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-tag.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
